--- a/dados/excel/unidade_tipo.xlsx
+++ b/dados/excel/unidade_tipo.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legenda — Tipos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +176,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -624,7 +636,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +657,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>vírgula</t>
+          <t>ponto e vírgula</t>
         </is>
       </c>
     </row>
@@ -669,7 +681,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -700,7 +712,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>tipo_unidade</t>
+          <t>﻿tipo_unidade</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -797,20 +809,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>tipo_unidade</t>
+          <t>﻿tipo_unidade</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -837,81 +849,157 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>unidade_fisica</t>
+          <t>Escola</t>
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>7107</v>
+        <v>5481</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>6285073838</v>
+        <v>51413027.87</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>884349.77</v>
+        <v>9380.227671957671</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>setor_operacional</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>139</v>
-      </c>
-      <c r="C3" s="10" t="n">
-        <v>3233</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>3494468933</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>1080875.02</v>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>3470</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>7414302.45</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>2136.68658501441</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>categoria_administrativa</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>3227</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>37961145.4</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>11763.60254105981</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1364</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>13745600.71</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>10077.41987536657</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>491</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>5785620.79</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>11783.3417311609</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>246</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>3904074.65</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>15870.22215447154</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>CMAE</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>669344.36</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>14241.36936170213</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>CAPS</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="C4" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>217096988</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>72365.66</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>outros</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>76</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>489</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>515862306</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1054933.14</v>
+      <c r="D9" s="15" t="n">
+        <v>387684.54</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>9230.584285714285</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -937,96 +1025,96 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Escola</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>UBS</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Setor</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>CAPS</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>CMAE</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t> </t>
         </is>
